--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="421">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseRequestGroup</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseRequestGroup</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-04-06T06:02:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1187,6 +1187,138 @@
   </si>
   <si>
     <t>Sub actions.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.extension:structured-rating</t>
+  </si>
+  <si>
+    <t>structured-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSStructuredRating}
+</t>
+  </si>
+  <si>
+    <t>PSS Rating Extension</t>
+  </si>
+  <si>
+    <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.prefix</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.title</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.description</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.textEquivalent</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.priority</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.code</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.documentation</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.kind</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.expression</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.actionId</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.relationship</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.offset[x]</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.timing[x]</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.participant</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.type</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.groupingBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.selectionBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.requiredBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.precheckBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.cardinalityBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.resource</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.action</t>
   </si>
 </sst>
 </file>
@@ -1496,12 +1628,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.50390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.50390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="56.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.73046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1509,7 +1641,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.2890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.93359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4539,10 +4671,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -8177,7 +8309,7 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>376</v>
@@ -8255,6 +8387,3736 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AC63" s="2"/>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:54+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:21:49+00:00</t>
+    <t>2025-04-17T08:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1631,17 +1631,17 @@
   <dimension ref="A1:AM95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.73046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.63671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.63671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.28515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1650,25 +1650,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="83.765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.81640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/branches/master/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
